--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136174079</v>
       </c>
       <c r="B3" t="n">
-        <v>92513</v>
+        <v>92516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136175409</v>
       </c>
       <c r="B7" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136174079</v>
       </c>
       <c r="B3" t="n">
-        <v>92516</v>
+        <v>92517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136175409</v>
       </c>
       <c r="B7" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136174079</v>
       </c>
       <c r="B3" t="n">
-        <v>92517</v>
+        <v>92522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136175409</v>
       </c>
       <c r="B7" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136174852</v>
       </c>
       <c r="B11" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>136174563</v>
       </c>
       <c r="B14" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>136174368</v>
       </c>
       <c r="B18" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>136174907</v>
       </c>
       <c r="B19" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30089-2026 artfynd.xlsx
+++ b/artfynd/A 30089-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136174079</v>
       </c>
       <c r="B3" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136175409</v>
       </c>
       <c r="B7" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
